--- a/Safe_Results/SA_Capacity_Costs/SA_Capacity_Costs_LPHB.xlsx
+++ b/Safe_Results/SA_Capacity_Costs/SA_Capacity_Costs_LPHB.xlsx
@@ -626,10 +626,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2628.05</v>
+        <v>1979.914</v>
       </c>
       <c r="G4" t="n">
-        <v>2439.661</v>
+        <v>1791.525</v>
       </c>
       <c r="H4" t="n">
         <v>188.389</v>
@@ -864,10 +864,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2706.049</v>
+        <v>2014.872</v>
       </c>
       <c r="G4" t="n">
-        <v>2521.42</v>
+        <v>1830.243</v>
       </c>
       <c r="H4" t="n">
         <v>184.629</v>
@@ -1102,10 +1102,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2706.049</v>
+        <v>2014.872</v>
       </c>
       <c r="G4" t="n">
-        <v>2521.42</v>
+        <v>1830.243</v>
       </c>
       <c r="H4" t="n">
         <v>184.629</v>
@@ -1340,10 +1340,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2706.049</v>
+        <v>2014.872</v>
       </c>
       <c r="G4" t="n">
-        <v>2521.42</v>
+        <v>1830.243</v>
       </c>
       <c r="H4" t="n">
         <v>184.629</v>
@@ -1578,10 +1578,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2656.859</v>
+        <v>1990.886</v>
       </c>
       <c r="G4" t="n">
-        <v>2467.622</v>
+        <v>1801.649</v>
       </c>
       <c r="H4" t="n">
         <v>189.237</v>
